--- a/Documentación/Empresa/Control de equipos.xlsx
+++ b/Documentación/Empresa/Control de equipos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\dta-agricola\Documentación\Empresa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTA-Agrícola\Documents\GitHub\dta-agricola\Documentación\Empresa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBE7E36-A807-4573-8B0A-159FDAD2FC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954ED3A6-8DDE-47A0-BD01-4059C931BAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="577" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="577" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movimiento contínuo" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="266">
   <si>
     <t>Observaciones</t>
   </si>
@@ -544,12 +544,6 @@
   </si>
   <si>
     <t>[28.405038, -106.895213]</t>
-  </si>
-  <si>
-    <t>{2, 3, 52, 625, 106, 0168}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo </t>
   </si>
   <si>
     <t>Cuenta</t>
@@ -825,17 +819,57 @@
   <si>
     <t>HW390(%)</t>
   </si>
+  <si>
+    <t>Número</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Sensor 1 bebes</t>
+  </si>
+  <si>
+    <t>0xF46A396</t>
+  </si>
+  <si>
+    <t>SHT</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>[29.050586, -107.412205]</t>
+  </si>
+  <si>
+    <t>Sensor 2 golden-rojo</t>
+  </si>
+  <si>
+    <t>Sensor 3 gala</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1004,7 +1038,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1061,12 +1095,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14993743705557422"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1116,110 +1144,110 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1228,14 +1256,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1243,22 +1268,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1270,115 +1289,115 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1387,94 +1406,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1486,148 +1487,185 @@
     <xf numFmtId="14" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1635,10 +1673,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9731,10 +9769,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2DF4C7FA-49D7-40E2-854D-2E837E8DF906}" name="Tabla4" displayName="Tabla4" ref="B16:C24" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2DF4C7FA-49D7-40E2-854D-2E837E8DF906}" name="Tabla4" displayName="Tabla4" ref="B16:C24" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="B16:C24" xr:uid="{2DF4C7FA-49D7-40E2-854D-2E837E8DF906}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8AB2FF7B-9F14-4281-B4FD-20D68724F54C}" name="T(h)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8AB2FF7B-9F14-4281-B4FD-20D68724F54C}" name="T(h)" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{EC5994F1-8001-487C-9692-AC5E36D247A0}" name="VWC(%)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10000,27 +10038,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="92" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" style="92" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" style="92" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" style="92" customWidth="1"/>
-    <col min="5" max="5" width="10" style="92" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" style="92" customWidth="1"/>
-    <col min="7" max="7" width="7.453125" style="92" customWidth="1"/>
-    <col min="8" max="8" width="8.453125" style="92" customWidth="1"/>
-    <col min="9" max="9" width="31.453125" style="92" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="92" customWidth="1"/>
-    <col min="11" max="11" width="37.81640625" style="92" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" style="92" customWidth="1"/>
-    <col min="13" max="13" width="20.453125" style="92" customWidth="1"/>
-    <col min="14" max="14" width="10.81640625" style="92" customWidth="1"/>
-    <col min="15" max="15" width="26.1796875" style="92" customWidth="1"/>
-    <col min="16" max="17" width="19.1796875" style="92" customWidth="1"/>
-    <col min="18" max="18" width="60.453125" style="93" customWidth="1"/>
-    <col min="19" max="26" width="12.1796875" style="49" customWidth="1"/>
-    <col min="27" max="16384" width="11.453125" style="92"/>
+    <col min="1" max="1" width="5.140625" style="89" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="89" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="89" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="89" customWidth="1"/>
+    <col min="5" max="5" width="10" style="89" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="89" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="89" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="89" customWidth="1"/>
+    <col min="9" max="9" width="31.42578125" style="89" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="89" customWidth="1"/>
+    <col min="11" max="11" width="37.85546875" style="89" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="89" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="89" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="89" customWidth="1"/>
+    <col min="15" max="15" width="26.140625" style="89" customWidth="1"/>
+    <col min="16" max="17" width="19.140625" style="89" customWidth="1"/>
+    <col min="18" max="18" width="60.42578125" style="90" customWidth="1"/>
+    <col min="19" max="26" width="12.140625" style="46" customWidth="1"/>
+    <col min="27" max="16384" width="11.42578125" style="89"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -10040,10 +10078,10 @@
       <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="58" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="37" t="s">
@@ -10088,7 +10126,7 @@
       <c r="Q2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="61" t="s">
+      <c r="R2" s="58" t="s">
         <v>16</v>
       </c>
       <c r="S2" s="37">
@@ -10116,976 +10154,976 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="59" customFormat="1">
-      <c r="A3" s="58">
+    <row r="3" spans="1:26" s="56" customFormat="1">
+      <c r="A3" s="55">
         <v>1</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="95">
+      <c r="C3" s="92">
         <v>526251106286</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="96" t="s">
+      <c r="F3" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="96">
+      <c r="G3" s="93">
         <v>1211</v>
       </c>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96" t="s">
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="118" t="s">
+      <c r="K3" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="58" t="s">
+      <c r="L3" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="58" t="s">
+      <c r="M3" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="N3" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="119" t="s">
+      <c r="O3" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="120">
+      <c r="P3" s="117">
         <v>43872</v>
       </c>
-      <c r="Q3" s="58" t="s">
+      <c r="Q3" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
-    </row>
-    <row r="4" spans="1:26" s="85" customFormat="1" ht="29">
-      <c r="A4" s="85">
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+    </row>
+    <row r="4" spans="1:26" s="82" customFormat="1" ht="30">
+      <c r="A4" s="82">
         <v>2</v>
       </c>
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="98">
+      <c r="C4" s="95">
         <v>526251271378</v>
       </c>
-      <c r="D4" s="99" t="s">
+      <c r="D4" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="99" t="s">
+      <c r="E4" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="99" t="s">
+      <c r="F4" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="99">
+      <c r="G4" s="96">
         <v>1211</v>
       </c>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99" t="s">
+      <c r="H4" s="96"/>
+      <c r="I4" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="99" t="s">
+      <c r="J4" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="121" t="s">
+      <c r="K4" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="85" t="s">
+      <c r="L4" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="85" t="s">
+      <c r="M4" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="85" t="s">
+      <c r="N4" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="122" t="s">
+      <c r="O4" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="123">
+      <c r="P4" s="120">
         <v>44603</v>
       </c>
-      <c r="Q4" s="85" t="s">
+      <c r="Q4" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="146" t="s">
+      <c r="R4" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-    </row>
-    <row r="5" spans="1:26" s="59" customFormat="1" ht="29">
-      <c r="A5" s="59">
+      <c r="S4" s="96"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="96"/>
+      <c r="V4" s="96"/>
+      <c r="W4" s="96"/>
+      <c r="X4" s="96"/>
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+    </row>
+    <row r="5" spans="1:26" s="56" customFormat="1" ht="30">
+      <c r="A5" s="56">
         <v>3</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="100">
+      <c r="C5" s="97">
         <v>526251024489</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="68">
+      <c r="G5" s="65">
         <v>1211</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68" t="s">
+      <c r="H5" s="65"/>
+      <c r="I5" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="J5" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="124" t="s">
+      <c r="K5" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="59" t="s">
+      <c r="L5" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="59" t="s">
+      <c r="M5" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="125" t="s">
+      <c r="O5" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="126">
+      <c r="P5" s="123">
         <v>44603</v>
       </c>
-      <c r="Q5" s="59" t="s">
+      <c r="Q5" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="R5" s="147" t="s">
+      <c r="R5" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-    </row>
-    <row r="6" spans="1:26" s="59" customFormat="1">
-      <c r="A6" s="59">
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+    </row>
+    <row r="6" spans="1:26" s="56" customFormat="1">
+      <c r="A6" s="56">
         <v>4</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="100">
+      <c r="C6" s="97">
         <v>526251452797</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="68">
+      <c r="G6" s="65">
         <v>1211</v>
       </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68" t="s">
+      <c r="H6" s="65"/>
+      <c r="I6" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="68" t="s">
+      <c r="J6" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="124" t="s">
+      <c r="K6" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="59" t="s">
+      <c r="L6" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="59" t="s">
+      <c r="M6" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="59" t="s">
+      <c r="N6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="125" t="s">
+      <c r="O6" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="126">
+      <c r="P6" s="123">
         <v>44603</v>
       </c>
-      <c r="Q6" s="59" t="s">
+      <c r="Q6" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="R6" s="147" t="s">
+      <c r="R6" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-      <c r="U6" s="68"/>
-      <c r="V6" s="68"/>
-      <c r="W6" s="68"/>
-      <c r="X6" s="68"/>
-      <c r="Y6" s="68"/>
-      <c r="Z6" s="68"/>
-    </row>
-    <row r="7" spans="1:26" s="59" customFormat="1">
-      <c r="A7" s="59">
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+    </row>
+    <row r="7" spans="1:26" s="56" customFormat="1">
+      <c r="A7" s="56">
         <v>5</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="100">
+      <c r="C7" s="97">
         <v>526255917395</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="68">
+      <c r="G7" s="65">
         <v>1211</v>
       </c>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68" t="s">
+      <c r="H7" s="65"/>
+      <c r="I7" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="68" t="s">
+      <c r="J7" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="124" t="s">
+      <c r="K7" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="59" t="s">
+      <c r="M7" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="N7" s="59" t="s">
+      <c r="N7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="125" t="s">
+      <c r="O7" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="P7" s="126">
+      <c r="P7" s="123">
         <v>44603</v>
       </c>
-      <c r="Q7" s="59" t="s">
+      <c r="Q7" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="147" t="s">
+      <c r="R7" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="68"/>
-      <c r="T7" s="68"/>
-      <c r="U7" s="68"/>
-      <c r="V7" s="68"/>
-      <c r="W7" s="68"/>
-      <c r="X7" s="68"/>
-      <c r="Y7" s="68"/>
-      <c r="Z7" s="68"/>
-    </row>
-    <row r="8" spans="1:26" s="59" customFormat="1">
-      <c r="A8" s="59" t="s">
+      <c r="S7" s="65"/>
+      <c r="T7" s="65"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65"/>
+      <c r="Z7" s="65"/>
+    </row>
+    <row r="8" spans="1:26" s="56" customFormat="1">
+      <c r="A8" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="100">
+      <c r="C8" s="97">
         <v>526251193016</v>
       </c>
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="68">
+      <c r="G8" s="65">
         <v>1211</v>
       </c>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68" t="s">
+      <c r="H8" s="65"/>
+      <c r="I8" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="68" t="s">
+      <c r="J8" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="124" t="s">
+      <c r="K8" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="59" t="s">
+      <c r="N8" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="125" t="s">
+      <c r="O8" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="126">
+      <c r="P8" s="123">
         <v>44603</v>
       </c>
-      <c r="Q8" s="59" t="s">
+      <c r="Q8" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="R8" s="147" t="s">
+      <c r="R8" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="S8" s="68"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="68"/>
-      <c r="V8" s="68"/>
-      <c r="W8" s="68"/>
-      <c r="X8" s="68"/>
-      <c r="Y8" s="68"/>
-      <c r="Z8" s="68"/>
-    </row>
-    <row r="9" spans="1:26" s="86" customFormat="1">
-      <c r="A9" s="86">
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="65"/>
+    </row>
+    <row r="9" spans="1:26" s="83" customFormat="1">
+      <c r="A9" s="83">
         <v>7</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="102">
+      <c r="C9" s="99">
         <v>526251342314</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="D9" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="103" t="s">
+      <c r="F9" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="103">
+      <c r="G9" s="100">
         <v>1211</v>
       </c>
-      <c r="H9" s="103" t="s">
+      <c r="H9" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="103" t="s">
+      <c r="I9" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="103" t="s">
+      <c r="J9" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="127" t="s">
+      <c r="K9" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="86" t="s">
+      <c r="L9" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="86" t="s">
+      <c r="M9" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="N9" s="86" t="s">
+      <c r="N9" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="O9" s="128" t="s">
+      <c r="O9" s="125" t="s">
         <v>69</v>
       </c>
-      <c r="P9" s="129">
+      <c r="P9" s="126">
         <v>44603</v>
       </c>
-      <c r="Q9" s="86" t="s">
+      <c r="Q9" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="R9" s="148" t="s">
+      <c r="R9" s="145" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="87" customFormat="1">
-      <c r="A10" s="87">
+    <row r="10" spans="1:26" s="84" customFormat="1">
+      <c r="A10" s="84">
         <v>8</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="105">
+      <c r="C10" s="102">
         <v>526251201079</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="D10" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="106" t="s">
+      <c r="E10" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="106" t="s">
+      <c r="F10" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="103">
         <v>1211</v>
       </c>
-      <c r="H10" s="106" t="s">
+      <c r="H10" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="106" t="s">
+      <c r="I10" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="106" t="s">
+      <c r="J10" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="K10" s="130" t="s">
+      <c r="K10" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="87" t="s">
+      <c r="L10" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="M10" s="87" t="s">
+      <c r="M10" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="O10" s="131" t="s">
+      <c r="O10" s="128" t="s">
         <v>78</v>
       </c>
-      <c r="P10" s="132">
+      <c r="P10" s="129">
         <v>44384</v>
       </c>
-      <c r="Q10" s="87" t="s">
+      <c r="Q10" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="R10" s="149" t="s">
+      <c r="R10" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="S10" s="106"/>
-      <c r="T10" s="106"/>
-      <c r="U10" s="106"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="106"/>
-      <c r="X10" s="106"/>
-      <c r="Y10" s="106"/>
-      <c r="Z10" s="106"/>
-    </row>
-    <row r="11" spans="1:26" s="88" customFormat="1">
-      <c r="A11" s="88">
+      <c r="S10" s="103"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
+      <c r="Y10" s="103"/>
+      <c r="Z10" s="103"/>
+    </row>
+    <row r="11" spans="1:26" s="85" customFormat="1">
+      <c r="A11" s="85">
         <v>9</v>
       </c>
-      <c r="B11" s="107" t="s">
+      <c r="B11" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="108">
+      <c r="C11" s="105">
         <v>526251020232</v>
       </c>
-      <c r="D11" s="109" t="s">
+      <c r="D11" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="109" t="s">
+      <c r="E11" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="109" t="s">
+      <c r="F11" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="106">
         <v>1312</v>
       </c>
-      <c r="H11" s="109" t="s">
+      <c r="H11" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="109" t="s">
+      <c r="I11" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="J11" s="133" t="s">
+      <c r="J11" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="134" t="s">
+      <c r="K11" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="134" t="s">
+      <c r="L11" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="M11" s="134" t="s">
+      <c r="M11" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="N11" s="134" t="s">
+      <c r="N11" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="O11" s="135" t="s">
+      <c r="O11" s="132" t="s">
         <v>86</v>
       </c>
-      <c r="P11" s="135">
+      <c r="P11" s="132">
         <v>44646</v>
       </c>
-      <c r="R11" s="150"/>
-      <c r="S11" s="109"/>
-      <c r="T11" s="109"/>
-      <c r="U11" s="109"/>
-      <c r="V11" s="109"/>
-      <c r="W11" s="109"/>
-      <c r="X11" s="109"/>
-      <c r="Y11" s="109"/>
-      <c r="Z11" s="109"/>
-    </row>
-    <row r="12" spans="1:26" s="86" customFormat="1">
-      <c r="A12" s="86">
+      <c r="R11" s="147"/>
+      <c r="S11" s="106"/>
+      <c r="T11" s="106"/>
+      <c r="U11" s="106"/>
+      <c r="V11" s="106"/>
+      <c r="W11" s="106"/>
+      <c r="X11" s="106"/>
+      <c r="Y11" s="106"/>
+      <c r="Z11" s="106"/>
+    </row>
+    <row r="12" spans="1:26" s="83" customFormat="1">
+      <c r="A12" s="83">
         <v>10</v>
       </c>
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="102">
+      <c r="C12" s="99">
         <v>526251531996</v>
       </c>
-      <c r="D12" s="103" t="s">
+      <c r="D12" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="103" t="s">
+      <c r="E12" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="103" t="s">
+      <c r="F12" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="100">
         <v>1211</v>
       </c>
-      <c r="H12" s="103" t="s">
+      <c r="H12" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="103" t="s">
+      <c r="I12" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="103" t="s">
+      <c r="J12" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="127" t="s">
+      <c r="K12" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="127" t="s">
+      <c r="L12" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="M12" s="127" t="s">
+      <c r="M12" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="N12" s="127" t="s">
+      <c r="N12" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="O12" s="136" t="s">
+      <c r="O12" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="P12" s="128">
+      <c r="P12" s="125">
         <v>44646</v>
       </c>
-      <c r="Q12" s="127"/>
-      <c r="R12" s="151" t="s">
+      <c r="Q12" s="124"/>
+      <c r="R12" s="148" t="s">
         <v>91</v>
       </c>
-      <c r="S12" s="103" t="s">
+      <c r="S12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="T12" s="103" t="s">
+      <c r="T12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="U12" s="103" t="s">
+      <c r="U12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="V12" s="103" t="s">
+      <c r="V12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="W12" s="103" t="s">
+      <c r="W12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="X12" s="103" t="s">
+      <c r="X12" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="Y12" s="103" t="s">
+      <c r="Y12" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="Z12" s="103" t="s">
+      <c r="Z12" s="100" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="59" customFormat="1">
-      <c r="A13" s="59">
+    <row r="13" spans="1:26" s="56" customFormat="1">
+      <c r="A13" s="56">
         <v>11</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="100">
+      <c r="C13" s="97">
         <v>526258372598</v>
       </c>
-      <c r="D13" s="68" t="s">
+      <c r="D13" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="E13" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="68" t="s">
+      <c r="F13" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="68">
+      <c r="G13" s="65">
         <v>1211</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="68" t="s">
+      <c r="I13" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="68" t="s">
+      <c r="J13" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="K13" s="124" t="s">
+      <c r="K13" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="124" t="s">
+      <c r="L13" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="M13" s="124" t="s">
+      <c r="M13" s="121" t="s">
         <v>97</v>
       </c>
-      <c r="N13" s="124" t="s">
+      <c r="N13" s="121" t="s">
         <v>85</v>
       </c>
-      <c r="O13" s="77" t="s">
+      <c r="O13" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="P13" s="125">
+      <c r="P13" s="122">
         <v>44646</v>
       </c>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="68"/>
-      <c r="V13" s="68"/>
-      <c r="W13" s="68"/>
-      <c r="X13" s="68"/>
-      <c r="Y13" s="68"/>
-      <c r="Z13" s="68"/>
-    </row>
-    <row r="14" spans="1:26" s="88" customFormat="1">
-      <c r="A14" s="88">
+      <c r="Q13" s="121"/>
+      <c r="R13" s="144"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+    </row>
+    <row r="14" spans="1:26" s="85" customFormat="1">
+      <c r="A14" s="85">
         <v>13</v>
       </c>
-      <c r="B14" s="107" t="s">
+      <c r="B14" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="110">
+      <c r="C14" s="107">
         <v>526251037317</v>
       </c>
-      <c r="D14" s="109" t="s">
+      <c r="D14" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="109" t="s">
+      <c r="E14" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="109" t="s">
+      <c r="F14" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="109">
+      <c r="G14" s="106">
         <v>1312</v>
       </c>
-      <c r="H14" s="109" t="s">
+      <c r="H14" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="109" t="s">
+      <c r="I14" s="106" t="s">
         <v>100</v>
       </c>
-      <c r="J14" s="109" t="s">
+      <c r="J14" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="134" t="s">
+      <c r="K14" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="134" t="s">
+      <c r="L14" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="M14" s="134" t="s">
+      <c r="M14" s="131" t="s">
         <v>101</v>
       </c>
-      <c r="N14" s="134" t="s">
+      <c r="N14" s="131" t="s">
         <v>102</v>
       </c>
-      <c r="O14" s="137" t="s">
+      <c r="O14" s="134" t="s">
         <v>103</v>
       </c>
-      <c r="P14" s="135">
+      <c r="P14" s="132">
         <v>44646</v>
       </c>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="152" t="s">
+      <c r="Q14" s="131"/>
+      <c r="R14" s="149" t="s">
         <v>104</v>
       </c>
-      <c r="S14" s="109"/>
-      <c r="T14" s="109"/>
-      <c r="U14" s="109"/>
-      <c r="V14" s="109"/>
-      <c r="W14" s="109"/>
-      <c r="X14" s="109"/>
-      <c r="Y14" s="109"/>
-      <c r="Z14" s="109"/>
-    </row>
-    <row r="15" spans="1:26" s="89" customFormat="1" ht="48" customHeight="1">
-      <c r="A15" s="111">
+      <c r="S14" s="106"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="106"/>
+      <c r="V14" s="106"/>
+      <c r="W14" s="106"/>
+      <c r="X14" s="106"/>
+      <c r="Y14" s="106"/>
+      <c r="Z14" s="106"/>
+    </row>
+    <row r="15" spans="1:26" s="86" customFormat="1" ht="48" customHeight="1">
+      <c r="A15" s="108">
         <v>14</v>
       </c>
-      <c r="B15" s="111" t="s">
+      <c r="B15" s="108" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="109">
         <v>526251060168</v>
       </c>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="113" t="s">
+      <c r="E15" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="113" t="s">
+      <c r="F15" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="110">
         <v>1211</v>
       </c>
-      <c r="H15" s="113" t="s">
+      <c r="H15" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="113" t="s">
+      <c r="I15" s="110" t="s">
         <v>106</v>
       </c>
-      <c r="J15" s="138" t="s">
+      <c r="J15" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="139" t="s">
+      <c r="K15" s="136" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="139" t="s">
+      <c r="L15" s="136" t="s">
         <v>83</v>
       </c>
-      <c r="M15" s="89" t="s">
+      <c r="M15" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="N15" s="89" t="s">
+      <c r="N15" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="O15" s="140" t="s">
+      <c r="O15" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="P15" s="141">
+      <c r="P15" s="138">
         <v>44762</v>
       </c>
-      <c r="Q15" s="139"/>
-      <c r="R15" s="153" t="s">
+      <c r="Q15" s="136"/>
+      <c r="R15" s="150" t="s">
         <v>109</v>
       </c>
-      <c r="S15" s="113"/>
-      <c r="T15" s="113"/>
-      <c r="U15" s="113"/>
-      <c r="V15" s="113"/>
-      <c r="W15" s="113"/>
-      <c r="X15" s="113"/>
-      <c r="Y15" s="113"/>
-      <c r="Z15" s="113"/>
-    </row>
-    <row r="16" spans="1:26" s="88" customFormat="1">
-      <c r="A16" s="88">
+      <c r="S15" s="110"/>
+      <c r="T15" s="110"/>
+      <c r="U15" s="110"/>
+      <c r="V15" s="110"/>
+      <c r="W15" s="110"/>
+      <c r="X15" s="110"/>
+      <c r="Y15" s="110"/>
+      <c r="Z15" s="110"/>
+    </row>
+    <row r="16" spans="1:26" s="85" customFormat="1">
+      <c r="A16" s="85">
         <v>15</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="104" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="110">
+      <c r="C16" s="107">
         <v>526251059200</v>
       </c>
-      <c r="D16" s="109" t="s">
+      <c r="D16" s="106" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="109" t="s">
+      <c r="E16" s="106" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="109" t="s">
+      <c r="F16" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="109">
+      <c r="G16" s="106">
         <v>1211</v>
       </c>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109" t="s">
+      <c r="H16" s="106"/>
+      <c r="I16" s="106" t="s">
         <v>113</v>
       </c>
-      <c r="J16" s="109" t="s">
+      <c r="J16" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="134" t="s">
+      <c r="K16" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="134" t="s">
+      <c r="L16" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="M16" s="134" t="s">
+      <c r="M16" s="131" t="s">
         <v>115</v>
       </c>
-      <c r="N16" s="134" t="s">
+      <c r="N16" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="O16" s="137" t="s">
+      <c r="O16" s="134" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="135">
+      <c r="P16" s="132">
         <v>44647</v>
       </c>
-      <c r="Q16" s="134"/>
-      <c r="R16" s="150"/>
-      <c r="S16" s="109"/>
-      <c r="T16" s="109"/>
-      <c r="U16" s="109"/>
-      <c r="V16" s="109"/>
-      <c r="W16" s="109"/>
-      <c r="X16" s="109"/>
-      <c r="Y16" s="109"/>
-      <c r="Z16" s="109"/>
-    </row>
-    <row r="17" spans="1:26" s="90" customFormat="1">
-      <c r="A17" s="90">
+      <c r="Q16" s="131"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="106"/>
+      <c r="T16" s="106"/>
+      <c r="U16" s="106"/>
+      <c r="V16" s="106"/>
+      <c r="W16" s="106"/>
+      <c r="X16" s="106"/>
+      <c r="Y16" s="106"/>
+      <c r="Z16" s="106"/>
+    </row>
+    <row r="17" spans="1:26" s="87" customFormat="1">
+      <c r="A17" s="87">
         <v>16</v>
       </c>
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="115">
+      <c r="C17" s="112">
         <v>526251020790</v>
       </c>
-      <c r="D17" s="116" t="s">
+      <c r="D17" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="116" t="s">
+      <c r="E17" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="116" t="s">
+      <c r="F17" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="116">
+      <c r="G17" s="113">
         <v>1211</v>
       </c>
-      <c r="H17" s="116"/>
-      <c r="I17" s="116" t="s">
+      <c r="H17" s="113"/>
+      <c r="I17" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="J17" s="116" t="s">
+      <c r="J17" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="142" t="s">
+      <c r="K17" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="142" t="s">
+      <c r="L17" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="142" t="s">
+      <c r="M17" s="139" t="s">
         <v>120</v>
       </c>
-      <c r="N17" s="142" t="s">
+      <c r="N17" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="O17" s="143" t="s">
+      <c r="O17" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="P17" s="144">
+      <c r="P17" s="141">
         <v>44647</v>
       </c>
-      <c r="R17" s="154"/>
-      <c r="S17" s="116"/>
-      <c r="T17" s="116"/>
-      <c r="U17" s="116"/>
-      <c r="V17" s="116"/>
-      <c r="W17" s="116"/>
-      <c r="X17" s="116"/>
-      <c r="Y17" s="116"/>
-      <c r="Z17" s="116"/>
-    </row>
-    <row r="18" spans="1:26" s="91" customFormat="1">
-      <c r="A18" s="86">
+      <c r="R17" s="151"/>
+      <c r="S17" s="113"/>
+      <c r="T17" s="113"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="113"/>
+      <c r="W17" s="113"/>
+      <c r="X17" s="113"/>
+      <c r="Y17" s="113"/>
+      <c r="Z17" s="113"/>
+    </row>
+    <row r="18" spans="1:26" s="88" customFormat="1">
+      <c r="A18" s="83">
         <v>17</v>
       </c>
-      <c r="B18" s="101" t="s">
+      <c r="B18" s="98" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="117">
+      <c r="C18" s="114">
         <v>526251020642</v>
       </c>
-      <c r="D18" s="103" t="s">
+      <c r="D18" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="103" t="s">
+      <c r="E18" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="103" t="s">
+      <c r="F18" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="103">
+      <c r="G18" s="100">
         <v>1211</v>
       </c>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103" t="s">
+      <c r="H18" s="100"/>
+      <c r="I18" s="100" t="s">
         <v>123</v>
       </c>
-      <c r="J18" s="145" t="s">
+      <c r="J18" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="127" t="s">
+      <c r="K18" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="155"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="103"/>
-      <c r="U18" s="103"/>
-      <c r="V18" s="103"/>
-      <c r="W18" s="103"/>
-      <c r="X18" s="103"/>
-      <c r="Y18" s="103"/>
-      <c r="Z18" s="103"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="83"/>
+      <c r="N18" s="83"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="152"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11099,34 +11137,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="39" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="39" customWidth="1"/>
     <col min="2" max="2" width="23" style="39" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" style="39" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" style="39" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="39" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="39" customWidth="1"/>
     <col min="5" max="5" width="10" style="39" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" style="39" customWidth="1"/>
-    <col min="7" max="7" width="24.453125" style="39" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="39" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" style="39" customWidth="1"/>
     <col min="8" max="8" width="14" style="39" customWidth="1"/>
-    <col min="9" max="9" width="39.453125" style="39" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" style="39" customWidth="1"/>
-    <col min="11" max="11" width="20.54296875" style="39" customWidth="1"/>
-    <col min="12" max="12" width="22.81640625" style="39" customWidth="1"/>
-    <col min="13" max="13" width="11.81640625" style="39" customWidth="1"/>
-    <col min="14" max="14" width="10.81640625" style="39" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" style="39" customWidth="1"/>
-    <col min="16" max="16" width="10.81640625" style="39" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" style="39" customWidth="1"/>
-    <col min="18" max="18" width="10.81640625" style="39" customWidth="1"/>
-    <col min="19" max="19" width="10.453125" style="39" customWidth="1"/>
-    <col min="20" max="21" width="19.1796875" style="39" customWidth="1"/>
-    <col min="22" max="22" width="60.453125" style="40" customWidth="1"/>
-    <col min="23" max="16384" width="11.453125" style="39"/>
+    <col min="9" max="9" width="39.42578125" style="39" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" style="39" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" style="39" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" style="39" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" style="39" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="39" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" style="39" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="39" customWidth="1"/>
+    <col min="17" max="17" width="10.42578125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="10.85546875" style="39" customWidth="1"/>
+    <col min="19" max="19" width="10.42578125" style="39" customWidth="1"/>
+    <col min="20" max="21" width="19.140625" style="39" customWidth="1"/>
+    <col min="22" max="22" width="60.42578125" style="40" customWidth="1"/>
+    <col min="23" max="16384" width="11.42578125" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
-      <c r="V1" s="61" t="s">
+      <c r="V1" s="58" t="s">
         <v>0</v>
       </c>
     </row>
@@ -11134,10 +11172,10 @@
       <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="58" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="37" t="s">
@@ -11194,57 +11232,57 @@
       <c r="U2" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="61" t="s">
+      <c r="V2" s="58" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="57" customFormat="1">
-      <c r="A3" s="57">
+    <row r="3" spans="1:30" s="54" customFormat="1">
+      <c r="A3" s="54">
         <v>1</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64" t="s">
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="62" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="74" t="s">
+      <c r="I3" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="L3" s="75" t="s">
+      <c r="L3" s="72" t="s">
         <v>138</v>
       </c>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="80">
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="77">
         <v>44603</v>
       </c>
-      <c r="U3" s="57" t="s">
+      <c r="U3" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="V3" s="81" t="s">
+      <c r="V3" s="78" t="s">
         <v>139</v>
       </c>
     </row>
@@ -11252,10 +11290,10 @@
       <c r="A4" s="38">
         <v>2</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="48">
         <v>526251020596</v>
       </c>
       <c r="D4" s="37" t="s">
@@ -11273,7 +11311,7 @@
       <c r="H4" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="45" t="s">
         <v>135</v>
       </c>
       <c r="J4" s="38" t="s">
@@ -11282,10 +11320,10 @@
       <c r="K4" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="V4" s="56"/>
+      <c r="V4" s="53"/>
       <c r="W4" s="37"/>
       <c r="X4" s="37"/>
       <c r="Y4" s="37"/>
@@ -11295,110 +11333,110 @@
       <c r="AC4" s="37"/>
       <c r="AD4" s="37"/>
     </row>
-    <row r="5" spans="1:30" s="58" customFormat="1">
-      <c r="A5" s="59">
+    <row r="5" spans="1:30" s="55" customFormat="1">
+      <c r="A5" s="56">
         <v>3</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="64">
         <v>526251020266</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="76" t="s">
+      <c r="I5" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="J5" s="59" t="s">
+      <c r="J5" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="K5" s="59" t="s">
+      <c r="K5" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="L5" s="77" t="s">
+      <c r="L5" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="V5" s="82"/>
-    </row>
-    <row r="6" spans="1:30" s="59" customFormat="1">
-      <c r="B6" s="69" t="s">
+      <c r="V5" s="79"/>
+    </row>
+    <row r="6" spans="1:30" s="56" customFormat="1">
+      <c r="B6" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="67">
         <v>526251579804</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="78" t="s">
+      <c r="I6" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="V6" s="83"/>
-    </row>
-    <row r="7" spans="1:30" s="60" customFormat="1">
-      <c r="B7" s="71" t="s">
+      <c r="V6" s="80"/>
+    </row>
+    <row r="7" spans="1:30" s="57" customFormat="1">
+      <c r="B7" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="72">
+      <c r="C7" s="69">
         <v>526251531996</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="H7" s="73" t="s">
+      <c r="H7" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="I7" s="79" t="s">
+      <c r="I7" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="J7" s="60" t="s">
+      <c r="J7" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="V7" s="84"/>
+      <c r="V7" s="81"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11415,37 +11453,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:V5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <dimension ref="A1:R31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" style="39" customWidth="1"/>
-    <col min="2" max="2" width="20" style="39" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" style="39" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" style="39" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" style="39" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" style="176" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="39" customWidth="1"/>
     <col min="5" max="5" width="10" style="39" customWidth="1"/>
-    <col min="6" max="6" width="22.81640625" style="39" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" style="39" customWidth="1"/>
-    <col min="8" max="8" width="36.54296875" style="39" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" style="39" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" style="39" customWidth="1"/>
-    <col min="11" max="11" width="22.81640625" style="39" customWidth="1"/>
-    <col min="12" max="13" width="10.453125" style="39" customWidth="1"/>
-    <col min="14" max="14" width="60.453125" style="40" customWidth="1"/>
-    <col min="15" max="16384" width="11.453125" style="39"/>
+    <col min="6" max="6" width="22.85546875" style="39" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="39" customWidth="1"/>
+    <col min="8" max="8" width="38.7109375" style="39" customWidth="1"/>
+    <col min="9" max="13" width="15.42578125" style="39" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" style="39" customWidth="1"/>
+    <col min="15" max="15" width="22.85546875" style="39" customWidth="1"/>
+    <col min="16" max="17" width="10.42578125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="60.42578125" style="40" customWidth="1"/>
+    <col min="19" max="16384" width="11.42578125" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="N1" s="39"/>
-    </row>
-    <row r="2" spans="1:22" s="37" customFormat="1">
+    <row r="1" spans="1:18">
+      <c r="R1" s="39"/>
+    </row>
+    <row r="2" spans="1:18" s="37" customFormat="1">
       <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="177" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>4</v>
@@ -11466,111 +11504,644 @@
         <v>12</v>
       </c>
       <c r="J2" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="L2" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="N2" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="O2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="P2" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="Q2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="R2" s="42" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:18" ht="14.25" customHeight="1">
       <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="178" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="43">
         <v>526251259145</v>
       </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45" t="s">
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44" t="s">
         <v>162</v>
       </c>
       <c r="G3" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="45" t="s">
         <v>164</v>
       </c>
       <c r="I3" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="N3" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="O3" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="L3" s="53">
+      <c r="P3" s="50">
         <v>45388</v>
       </c>
-      <c r="M3" s="53">
+      <c r="Q3" s="50">
         <v>45753</v>
       </c>
-      <c r="N3" s="54"/>
-    </row>
-    <row r="4" spans="1:22" s="38" customFormat="1">
-      <c r="B4" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="48">
-        <v>526251060168</v>
-      </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="K4" s="55"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="R3" s="51"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="B4" s="179"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="45"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="51"/>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="38"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="180">
+        <v>20333844254</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="I5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J5" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="L5" s="182" t="s">
+        <v>262</v>
+      </c>
+      <c r="M5" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="O5" s="38"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="38"/>
+      <c r="B6" s="180"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="I6"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153" t="s">
+        <v>260</v>
+      </c>
+      <c r="L6" s="182" t="s">
+        <v>261</v>
+      </c>
+      <c r="M6" s="161"/>
+      <c r="N6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O6" s="38" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="38"/>
+      <c r="B7" s="180"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="I7"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="182" t="s">
+        <v>261</v>
+      </c>
+      <c r="M7" s="161"/>
+      <c r="N7" t="s">
+        <v>264</v>
+      </c>
+      <c r="O7" s="38"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="38"/>
+      <c r="B8" s="180"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="I8"/>
+      <c r="J8" s="153"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="182" t="s">
+        <v>261</v>
+      </c>
+      <c r="M8" s="161"/>
+      <c r="N8" t="s">
+        <v>265</v>
+      </c>
+      <c r="O8" s="38"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="38"/>
+      <c r="B9" s="180"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="I9"/>
+      <c r="J9" s="153"/>
+      <c r="K9" s="153"/>
+      <c r="L9" s="182" t="s">
+        <v>261</v>
+      </c>
+      <c r="M9" s="161"/>
+      <c r="N9"/>
+      <c r="O9" s="38"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="38"/>
+      <c r="B10" s="180"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="I10"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="182" t="s">
+        <v>261</v>
+      </c>
+      <c r="M10" s="161"/>
+      <c r="N10"/>
+      <c r="O10" s="38"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="B11" s="180">
+        <v>24430362948</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11" s="160"/>
+      <c r="N11" s="157" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="B12" s="180">
+        <v>24530080316</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="I12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J12" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N12" s="153" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="B13" s="180">
+        <v>24530080324</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="I13" t="s">
+        <v>191</v>
+      </c>
+      <c r="J13" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K13" s="153"/>
+      <c r="L13" s="153"/>
+      <c r="M13" s="162">
+        <v>45970</v>
+      </c>
+      <c r="N13" s="153" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="B14" s="180">
+        <v>24530080332</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="I14" t="s">
+        <v>192</v>
+      </c>
+      <c r="J14" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="160"/>
+      <c r="N14" s="165" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15" s="180">
+        <v>24530080407</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15" s="160"/>
+      <c r="N15" s="157" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16" s="180">
+        <v>24530080415</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="I16" t="s">
+        <v>193</v>
+      </c>
+      <c r="J16" s="153" t="s">
+        <v>204</v>
+      </c>
+      <c r="K16" s="153"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="160"/>
+      <c r="N16" s="153" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="180">
+        <v>24530080423</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="I17" s="153" t="s">
+        <v>229</v>
+      </c>
+      <c r="J17" s="153" t="s">
+        <v>203</v>
+      </c>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="160"/>
+      <c r="N17" s="153" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="180">
+        <v>24530080431</v>
+      </c>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="I18" s="153" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" s="153" t="s">
+        <v>204</v>
+      </c>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="160"/>
+      <c r="N18" s="153" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="180">
+        <v>24530080449</v>
+      </c>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="I19" t="s">
+        <v>195</v>
+      </c>
+      <c r="J19" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K19" s="153"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="160"/>
+      <c r="N19"/>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="180">
+        <v>24530080456</v>
+      </c>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="I20" t="s">
+        <v>196</v>
+      </c>
+      <c r="J20" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N20" s="153" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="180">
+        <v>24530094119</v>
+      </c>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="I21" t="s">
+        <v>197</v>
+      </c>
+      <c r="J21" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K21" s="153"/>
+      <c r="L21" s="153"/>
+      <c r="M21" s="160"/>
+      <c r="N21" s="153" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="180">
+        <v>24530094127</v>
+      </c>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="I22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22" s="160"/>
+      <c r="N22" s="160"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="181">
+        <v>24530094134</v>
+      </c>
+      <c r="C23" s="163"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="163"/>
+      <c r="F23" s="163"/>
+      <c r="I23" s="163"/>
+      <c r="J23" s="163"/>
+      <c r="K23" s="163"/>
+      <c r="L23" s="163"/>
+      <c r="M23" s="164"/>
+      <c r="N23" s="166" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="180">
+        <v>24530094135</v>
+      </c>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="I24" t="s">
+        <v>235</v>
+      </c>
+      <c r="J24" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K24" s="153"/>
+      <c r="L24" s="153"/>
+      <c r="M24" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N24" s="153" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="180">
+        <v>24530094143</v>
+      </c>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="I25" s="153" t="s">
+        <v>224</v>
+      </c>
+      <c r="J25" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="K25" s="153"/>
+      <c r="L25" s="153"/>
+      <c r="M25" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N25"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="180">
+        <v>24530094150</v>
+      </c>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="I26" s="153" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="K26" s="153"/>
+      <c r="L26" s="153"/>
+      <c r="M26" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N26"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="180">
+        <v>24530094267</v>
+      </c>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="I27" t="s">
+        <v>198</v>
+      </c>
+      <c r="J27" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K27" s="153"/>
+      <c r="L27" s="153"/>
+      <c r="M27" s="162">
+        <v>45912</v>
+      </c>
+      <c r="N27"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="180">
+        <v>24530094275</v>
+      </c>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="I28" t="s">
+        <v>199</v>
+      </c>
+      <c r="J28" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="K28" s="153"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N28" s="153" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="180">
+        <v>24530094283</v>
+      </c>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="I29" t="s">
+        <v>200</v>
+      </c>
+      <c r="J29" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="K29" s="153"/>
+      <c r="L29" s="153"/>
+      <c r="M29" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N29" s="153" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="180">
+        <v>24530094291</v>
+      </c>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="I30" s="153" t="s">
+        <v>222</v>
+      </c>
+      <c r="J30" s="153" t="s">
+        <v>203</v>
+      </c>
+      <c r="K30" s="153"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N30" s="153" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="180">
+        <v>24530094309</v>
+      </c>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="I31" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="153" t="s">
+        <v>131</v>
+      </c>
+      <c r="K31" s="153"/>
+      <c r="L31" s="153"/>
+      <c r="M31" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="N31" s="153" t="s">
+        <v>228</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="H4" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -11580,25 +12151,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.81640625" customWidth="1"/>
-    <col min="6" max="6" width="33.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" customWidth="1"/>
-    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.85546875" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" ht="30">
       <c r="A1" s="22" t="s">
         <v>2</v>
       </c>
@@ -11606,43 +12177,43 @@
         <v>3</v>
       </c>
       <c r="C1" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="H1" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>176</v>
-      </c>
       <c r="J1" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L1" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M1" s="22" t="s">
         <v>131</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>87</v>
       </c>
@@ -11656,19 +12227,19 @@
         <v>18</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="F2" s="158" t="s">
-        <v>220</v>
-      </c>
-      <c r="G2" s="158" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="155" t="s">
+        <v>218</v>
+      </c>
+      <c r="G2" s="155" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="161">
+      <c r="H2" s="158">
         <v>45933</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
+    <row r="3" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>161</v>
       </c>
@@ -11682,21 +12253,21 @@
         <v>18</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="158" t="s">
-        <v>221</v>
-      </c>
-      <c r="H3" s="161">
+        <v>180</v>
+      </c>
+      <c r="G3" s="155" t="s">
+        <v>219</v>
+      </c>
+      <c r="H3" s="158">
         <v>45904</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
-      <c r="A4" s="170" t="s">
-        <v>235</v>
+    <row r="4" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A4" s="167" t="s">
+        <v>233</v>
       </c>
       <c r="B4" s="35">
         <v>526251201079</v>
@@ -11708,19 +12279,19 @@
         <v>32</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="159" t="s">
-        <v>222</v>
-      </c>
-      <c r="G4" s="159" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" s="161">
+        <v>175</v>
+      </c>
+      <c r="F4" s="156" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="156" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="158">
         <v>45780</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
+    <row r="5" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>140</v>
       </c>
@@ -11728,36 +12299,36 @@
         <v>526251020596</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" s="155" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="155" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="159" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="158" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="158" t="s">
-        <v>131</v>
-      </c>
-      <c r="H5" s="162" t="s">
-        <v>179</v>
-      </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="H6" s="163"/>
+      <c r="H6" s="160"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7">
         <v>20333844254</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G7" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H7" s="164" t="s">
-        <v>178</v>
+        <v>189</v>
+      </c>
+      <c r="G7" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H7" s="161" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -11765,11 +12336,11 @@
         <v>24430362948</v>
       </c>
       <c r="E8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="163"/>
-      <c r="I8" s="160" t="s">
-        <v>225</v>
+        <v>175</v>
+      </c>
+      <c r="H8" s="160"/>
+      <c r="I8" s="157" t="s">
+        <v>223</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -11780,19 +12351,19 @@
         <v>24530080316</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
-        <v>192</v>
-      </c>
-      <c r="G9" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H9" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="156" t="s">
-        <v>208</v>
+        <v>190</v>
+      </c>
+      <c r="G9" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H9" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" s="153" t="s">
+        <v>206</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -11803,19 +12374,19 @@
         <v>24530080324</v>
       </c>
       <c r="E10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
-        <v>193</v>
-      </c>
-      <c r="G10" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H10" s="165">
+        <v>191</v>
+      </c>
+      <c r="G10" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H10" s="162">
         <v>45970</v>
       </c>
-      <c r="I10" s="156" t="s">
-        <v>211</v>
+      <c r="I10" s="153" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -11823,17 +12394,17 @@
         <v>24530080332</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
-      </c>
-      <c r="G11" s="156" t="s">
-        <v>207</v>
-      </c>
-      <c r="H11" s="163"/>
-      <c r="I11" s="168" t="s">
-        <v>233</v>
+        <v>192</v>
+      </c>
+      <c r="G11" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="H11" s="160"/>
+      <c r="I11" s="165" t="s">
+        <v>231</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -11847,11 +12418,11 @@
         <v>24530080407</v>
       </c>
       <c r="E12" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="163"/>
-      <c r="I12" s="160" t="s">
-        <v>232</v>
+        <v>175</v>
+      </c>
+      <c r="H12" s="160"/>
+      <c r="I12" s="157" t="s">
+        <v>230</v>
       </c>
       <c r="J12">
         <v>3</v>
@@ -11862,17 +12433,17 @@
         <v>24530080415</v>
       </c>
       <c r="E13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F13" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="156" t="s">
-        <v>206</v>
-      </c>
-      <c r="H13" s="163"/>
-      <c r="I13" s="156" t="s">
-        <v>210</v>
+        <v>193</v>
+      </c>
+      <c r="G13" s="153" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" s="160"/>
+      <c r="I13" s="153" t="s">
+        <v>208</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -11883,17 +12454,17 @@
         <v>24530080423</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
-      </c>
-      <c r="F14" s="156" t="s">
-        <v>231</v>
-      </c>
-      <c r="G14" s="156" t="s">
-        <v>205</v>
-      </c>
-      <c r="H14" s="163"/>
-      <c r="I14" s="156" t="s">
-        <v>210</v>
+        <v>175</v>
+      </c>
+      <c r="F14" s="153" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="153" t="s">
+        <v>203</v>
+      </c>
+      <c r="H14" s="160"/>
+      <c r="I14" s="153" t="s">
+        <v>208</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -11904,17 +12475,17 @@
         <v>24530080431</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F15" s="156" t="s">
-        <v>196</v>
-      </c>
-      <c r="G15" s="156" t="s">
-        <v>206</v>
-      </c>
-      <c r="H15" s="163"/>
-      <c r="I15" s="156" t="s">
-        <v>218</v>
+        <v>175</v>
+      </c>
+      <c r="F15" s="153" t="s">
+        <v>194</v>
+      </c>
+      <c r="G15" s="153" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" s="160"/>
+      <c r="I15" s="153" t="s">
+        <v>216</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -11925,34 +12496,34 @@
         <v>24530080449</v>
       </c>
       <c r="E16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F16" t="s">
-        <v>197</v>
-      </c>
-      <c r="G16" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H16" s="163"/>
+        <v>195</v>
+      </c>
+      <c r="G16" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H16" s="160"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17">
         <v>24530080456</v>
       </c>
       <c r="E17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F17" t="s">
-        <v>198</v>
-      </c>
-      <c r="G17" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H17" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I17" s="156" t="s">
-        <v>209</v>
+        <v>196</v>
+      </c>
+      <c r="G17" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H17" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="153" t="s">
+        <v>207</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -11963,17 +12534,17 @@
         <v>24530094119</v>
       </c>
       <c r="E18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F18" t="s">
-        <v>199</v>
-      </c>
-      <c r="G18" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H18" s="163"/>
-      <c r="I18" s="156" t="s">
-        <v>214</v>
+        <v>197</v>
+      </c>
+      <c r="G18" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H18" s="160"/>
+      <c r="I18" s="153" t="s">
+        <v>212</v>
       </c>
       <c r="K18">
         <v>2</v>
@@ -11984,38 +12555,38 @@
         <v>24530094127</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
-        <v>236</v>
-      </c>
-      <c r="H19" s="163"/>
-      <c r="I19" s="163"/>
+        <v>234</v>
+      </c>
+      <c r="H19" s="160"/>
+      <c r="I19" s="160"/>
       <c r="N19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="166">
+      <c r="A20" s="163">
         <v>24530094134</v>
       </c>
-      <c r="B20" s="166"/>
-      <c r="C20" s="166"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="166" t="s">
-        <v>177</v>
-      </c>
-      <c r="F20" s="166"/>
-      <c r="G20" s="166"/>
-      <c r="H20" s="167"/>
-      <c r="I20" s="169" t="s">
-        <v>234</v>
-      </c>
-      <c r="J20" s="166"/>
-      <c r="K20" s="166"/>
-      <c r="L20" s="166"/>
-      <c r="M20" s="166"/>
-      <c r="N20" s="166">
+      <c r="B20" s="163"/>
+      <c r="C20" s="163"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="163" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" s="163"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="164"/>
+      <c r="I20" s="166" t="s">
+        <v>232</v>
+      </c>
+      <c r="J20" s="163"/>
+      <c r="K20" s="163"/>
+      <c r="L20" s="163"/>
+      <c r="M20" s="163"/>
+      <c r="N20" s="163">
         <v>1</v>
       </c>
     </row>
@@ -12024,19 +12595,19 @@
         <v>24530094135</v>
       </c>
       <c r="E21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F21" t="s">
-        <v>237</v>
-      </c>
-      <c r="G21" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H21" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="156" t="s">
-        <v>219</v>
+        <v>235</v>
+      </c>
+      <c r="G21" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H21" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I21" s="153" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -12044,16 +12615,16 @@
         <v>24530094143</v>
       </c>
       <c r="E22" t="s">
-        <v>177</v>
-      </c>
-      <c r="F22" s="156" t="s">
-        <v>226</v>
-      </c>
-      <c r="G22" s="156" t="s">
-        <v>207</v>
-      </c>
-      <c r="H22" s="164" t="s">
-        <v>178</v>
+        <v>175</v>
+      </c>
+      <c r="F22" s="153" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="H22" s="161" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -12061,16 +12632,16 @@
         <v>24530094150</v>
       </c>
       <c r="E23" t="s">
-        <v>177</v>
-      </c>
-      <c r="F23" s="156" t="s">
-        <v>227</v>
-      </c>
-      <c r="G23" s="156" t="s">
-        <v>207</v>
-      </c>
-      <c r="H23" s="164" t="s">
-        <v>178</v>
+        <v>175</v>
+      </c>
+      <c r="F23" s="153" t="s">
+        <v>225</v>
+      </c>
+      <c r="G23" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="H23" s="161" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -12078,15 +12649,15 @@
         <v>24530094267</v>
       </c>
       <c r="E24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
-        <v>200</v>
-      </c>
-      <c r="G24" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H24" s="165">
+        <v>198</v>
+      </c>
+      <c r="G24" s="153" t="s">
+        <v>202</v>
+      </c>
+      <c r="H24" s="162">
         <v>45912</v>
       </c>
     </row>
@@ -12095,19 +12666,19 @@
         <v>24530094275</v>
       </c>
       <c r="E25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F25" t="s">
-        <v>201</v>
-      </c>
-      <c r="G25" s="156" t="s">
-        <v>207</v>
-      </c>
-      <c r="H25" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I25" s="156" t="s">
-        <v>229</v>
+        <v>199</v>
+      </c>
+      <c r="G25" s="153" t="s">
+        <v>205</v>
+      </c>
+      <c r="H25" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="153" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -12115,19 +12686,19 @@
         <v>24530094283</v>
       </c>
       <c r="E26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F26" t="s">
+        <v>200</v>
+      </c>
+      <c r="G26" s="153" t="s">
         <v>202</v>
       </c>
-      <c r="G26" s="156" t="s">
-        <v>204</v>
-      </c>
-      <c r="H26" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="156" t="s">
-        <v>228</v>
+      <c r="H26" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I26" s="153" t="s">
+        <v>226</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -12138,19 +12709,19 @@
         <v>24530094291</v>
       </c>
       <c r="E27" t="s">
-        <v>177</v>
-      </c>
-      <c r="F27" s="156" t="s">
-        <v>224</v>
-      </c>
-      <c r="G27" s="156" t="s">
-        <v>205</v>
-      </c>
-      <c r="H27" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="156" t="s">
-        <v>229</v>
+        <v>175</v>
+      </c>
+      <c r="F27" s="153" t="s">
+        <v>222</v>
+      </c>
+      <c r="G27" s="153" t="s">
+        <v>203</v>
+      </c>
+      <c r="H27" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="153" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -12158,19 +12729,19 @@
         <v>24530094309</v>
       </c>
       <c r="E28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s">
-        <v>203</v>
-      </c>
-      <c r="G28" s="156" t="s">
+        <v>201</v>
+      </c>
+      <c r="G28" s="153" t="s">
         <v>131</v>
       </c>
-      <c r="H28" s="164" t="s">
-        <v>178</v>
-      </c>
-      <c r="I28" s="156" t="s">
-        <v>230</v>
+      <c r="H28" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="I28" s="153" t="s">
+        <v>228</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -12181,74 +12752,74 @@
         <v>24330165126</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="I31" s="157" t="s">
-        <v>217</v>
-      </c>
-      <c r="J31" s="157">
+      <c r="I31" s="154" t="s">
+        <v>215</v>
+      </c>
+      <c r="J31" s="154">
         <f>SUM(J2:J30)</f>
         <v>22</v>
       </c>
-      <c r="K31" s="157">
+      <c r="K31" s="154">
         <f t="shared" ref="K31:M31" si="0">SUM(K2:K30)</f>
         <v>2</v>
       </c>
-      <c r="L31" s="157">
+      <c r="L31" s="154">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M31" s="157">
+      <c r="M31" s="154">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="N31" s="157">
+      <c r="N31" s="154">
         <f>SUM(N2:N30)</f>
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="I32" s="156"/>
+      <c r="I32" s="153"/>
     </row>
     <row r="33" spans="9:9">
-      <c r="I33" s="156"/>
+      <c r="I33" s="153"/>
     </row>
     <row r="35" spans="9:9">
-      <c r="I35" s="156"/>
+      <c r="I35" s="153"/>
     </row>
     <row r="36" spans="9:9">
-      <c r="I36" s="156"/>
+      <c r="I36" s="153"/>
     </row>
     <row r="38" spans="9:9">
-      <c r="I38" s="156"/>
+      <c r="I38" s="153"/>
     </row>
     <row r="39" spans="9:9">
-      <c r="I39" s="156"/>
+      <c r="I39" s="153"/>
     </row>
     <row r="40" spans="9:9">
-      <c r="I40" s="156"/>
+      <c r="I40" s="153"/>
     </row>
     <row r="42" spans="9:9">
-      <c r="I42" s="156"/>
+      <c r="I42" s="153"/>
     </row>
     <row r="44" spans="9:9">
-      <c r="I44" s="156"/>
+      <c r="I44" s="153"/>
     </row>
     <row r="45" spans="9:9">
-      <c r="I45" s="156"/>
+      <c r="I45" s="153"/>
     </row>
     <row r="47" spans="9:9">
-      <c r="I47" s="156"/>
+      <c r="I47" s="153"/>
     </row>
     <row r="48" spans="9:9">
-      <c r="I48" s="156"/>
+      <c r="I48" s="153"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="I49" s="156"/>
-    </row>
-    <row r="51" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+      <c r="I49" s="153"/>
+    </row>
+    <row r="51" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A51" s="18" t="s">
         <v>18</v>
       </c>
@@ -12262,22 +12833,22 @@
         <v>18</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G51" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I51" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H51" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I51" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="52" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A52" s="24" t="s">
         <v>39</v>
       </c>
@@ -12291,22 +12862,22 @@
         <v>18</v>
       </c>
       <c r="E52" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F52" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52" s="18" t="s">
+      <c r="I52" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H52" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I52" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="53" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A53" s="24" t="s">
         <v>94</v>
       </c>
@@ -12320,22 +12891,22 @@
         <v>18</v>
       </c>
       <c r="E53" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F53" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="G53" s="18" t="s">
+      <c r="I53" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H53" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I53" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="54" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A54" s="24" t="s">
         <v>50</v>
       </c>
@@ -12349,22 +12920,22 @@
         <v>18</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>52</v>
       </c>
       <c r="G54" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I54" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H54" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I54" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="55" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A55" s="24" t="s">
         <v>30</v>
       </c>
@@ -12378,22 +12949,22 @@
         <v>18</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G55" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H55" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I55" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="56" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A56" s="24" t="s">
         <v>56</v>
       </c>
@@ -12407,22 +12978,22 @@
         <v>18</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>58</v>
       </c>
       <c r="G56" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I56" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H56" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I56" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="57" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A57" s="24" t="s">
         <v>45</v>
       </c>
@@ -12436,22 +13007,22 @@
         <v>32</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>47</v>
       </c>
       <c r="G57" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H57" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I57" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="58" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A58" s="24" t="s">
         <v>153</v>
       </c>
@@ -12465,19 +13036,19 @@
         <v>32</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>157</v>
       </c>
       <c r="G58" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="I58" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="I58" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="59" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A59" s="18" t="s">
         <v>118</v>
       </c>
@@ -12485,19 +13056,19 @@
         <v>526251020790</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>120</v>
       </c>
       <c r="G59" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="I59" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="I59" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="60" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
       <c r="A60" s="18" t="s">
         <v>147</v>
       </c>
@@ -12505,22 +13076,22 @@
         <v>526251020266</v>
       </c>
       <c r="E60" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="H60" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F60" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="G60" s="18" t="s">
+      <c r="I60" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="H60" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="I60" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="20" customFormat="1" ht="14.15" customHeight="1">
+    </row>
+    <row r="62" spans="1:9" s="20" customFormat="1" ht="14.1" customHeight="1">
       <c r="A62" s="29" t="s">
         <v>110</v>
       </c>
@@ -12534,7 +13105,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F62" s="20" t="s">
         <v>115</v>
@@ -12543,7 +13114,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="20" customFormat="1" ht="14.15" customHeight="1">
+    <row r="63" spans="1:9" s="20" customFormat="1" ht="14.1" customHeight="1">
       <c r="A63" s="29" t="s">
         <v>99</v>
       </c>
@@ -12557,7 +13128,7 @@
         <v>32</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F63" s="20" t="s">
         <v>101</v>
@@ -12566,7 +13137,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="20" customFormat="1" ht="14.15" customHeight="1">
+    <row r="64" spans="1:9" s="20" customFormat="1" ht="14.1" customHeight="1">
       <c r="A64" s="29" t="s">
         <v>80</v>
       </c>
@@ -12576,7 +13147,7 @@
       <c r="C64" s="31"/>
       <c r="D64" s="31"/>
       <c r="E64" s="31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F64" s="20" t="s">
         <v>84</v>
@@ -12585,7 +13156,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="21" customFormat="1" ht="14.15" customHeight="1">
+    <row r="65" spans="1:9" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A65" s="32" t="s">
         <v>61</v>
       </c>
@@ -12599,19 +13170,19 @@
         <v>32</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G65" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" s="21" customFormat="1" ht="14.15" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A66" s="21" t="s">
         <v>122</v>
       </c>
@@ -12619,20 +13190,20 @@
         <v>526251020642</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G66" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="I66" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="I66" s="21" t="s">
-        <v>180</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -12641,18 +13212,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.26953125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>12</v>
@@ -12670,9 +13242,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15">
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>24</v>
@@ -12690,9 +13262,9 @@
         <v>43872</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15">
+    <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>35</v>
@@ -12710,9 +13282,9 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>35</v>
@@ -12730,9 +13302,9 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15">
+    <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>35</v>
@@ -12750,9 +13322,9 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15">
+    <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>35</v>
@@ -12770,9 +13342,9 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15">
+    <row r="7" spans="1:6">
       <c r="A7" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>35</v>
@@ -12790,9 +13362,9 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15">
+    <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>66</v>
@@ -12810,9 +13382,9 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15">
+    <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>76</v>
@@ -12828,9 +13400,9 @@
         <v>44384</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15">
+    <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>83</v>
@@ -12848,9 +13420,9 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15">
+    <row r="11" spans="1:6">
       <c r="A11" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>83</v>
@@ -12868,9 +13440,9 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15">
+    <row r="12" spans="1:6">
       <c r="A12" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>83</v>
@@ -12888,9 +13460,9 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15">
+    <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>83</v>
@@ -12908,9 +13480,9 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15">
+    <row r="14" spans="1:6">
       <c r="A14" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>83</v>
@@ -12928,9 +13500,9 @@
         <v>44762</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15">
+    <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>114</v>
@@ -12948,9 +13520,9 @@
         <v>44647</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15">
+    <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>114</v>
@@ -12968,15 +13540,15 @@
         <v>44647</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15">
+    <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>136</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="14" t="s">
@@ -12984,9 +13556,9 @@
       </c>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="15">
+    <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>144</v>
@@ -13000,9 +13572,9 @@
       </c>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" ht="15">
+    <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>150</v>
@@ -13016,9 +13588,9 @@
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="15">
+    <row r="20" spans="1:6">
       <c r="A20" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>157</v>
@@ -13030,9 +13602,9 @@
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
     </row>
-    <row r="21" spans="1:6" ht="15">
+    <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>165</v>
@@ -13070,234 +13642,234 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D02258-BB1F-41F1-B649-95B4395F579C}">
   <dimension ref="A2:H24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
-    <col min="3" max="5" width="11.7265625" customWidth="1"/>
-    <col min="6" max="6" width="55.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="55.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="21">
-      <c r="B2" s="177" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
+      <c r="B2" s="174" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="176" t="s">
-        <v>253</v>
-      </c>
-      <c r="B3" s="176" t="s">
+      <c r="A3" s="173" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="173" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="172" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="174" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="173"/>
+      <c r="B4" s="173"/>
+      <c r="C4" s="154" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="154" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" s="154" t="s">
         <v>241</v>
       </c>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="176"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="157" t="s">
-        <v>240</v>
-      </c>
-      <c r="D4" s="157" t="s">
+      <c r="F4" s="172"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="168"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="175">
+        <v>0</v>
+      </c>
+      <c r="B5" s="169">
+        <v>0</v>
+      </c>
+      <c r="C5" s="169">
+        <v>40</v>
+      </c>
+      <c r="D5" s="169">
+        <v>50</v>
+      </c>
+      <c r="E5" s="169">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="175"/>
+      <c r="B6" s="169">
+        <v>6</v>
+      </c>
+      <c r="C6" s="169">
+        <v>35</v>
+      </c>
+      <c r="D6" s="169">
+        <v>48</v>
+      </c>
+      <c r="E6" s="169">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="174"/>
-      <c r="G4" s="172"/>
-      <c r="H4" s="172"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="178">
-        <v>0</v>
-      </c>
-      <c r="B5" s="173">
-        <v>0</v>
-      </c>
-      <c r="C5" s="173">
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="175"/>
+      <c r="B7" s="169">
+        <v>24</v>
+      </c>
+      <c r="C7" s="169">
+        <v>25</v>
+      </c>
+      <c r="D7" s="169">
+        <v>35</v>
+      </c>
+      <c r="E7" s="169">
         <v>40</v>
       </c>
-      <c r="D5" s="173">
-        <v>50</v>
-      </c>
-      <c r="E5" s="173">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
         <v>244</v>
       </c>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="178"/>
-      <c r="B6" s="173">
-        <v>6</v>
-      </c>
-      <c r="C6" s="173">
-        <v>35</v>
-      </c>
-      <c r="D6" s="173">
-        <v>48</v>
-      </c>
-      <c r="E6" s="173">
-        <v>58</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="175"/>
+      <c r="B8" s="169">
+        <v>72</v>
+      </c>
+      <c r="C8" s="169">
+        <v>20</v>
+      </c>
+      <c r="D8" s="169">
+        <v>30</v>
+      </c>
+      <c r="E8" s="169">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
         <v>245</v>
       </c>
-      <c r="G6" s="173"/>
-      <c r="H6" s="173"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="178"/>
-      <c r="B7" s="173">
-        <v>24</v>
-      </c>
-      <c r="C7" s="173">
-        <v>25</v>
-      </c>
-      <c r="D7" s="173">
-        <v>35</v>
-      </c>
-      <c r="E7" s="173">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>246</v>
-      </c>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="178"/>
-      <c r="B8" s="173">
-        <v>72</v>
-      </c>
-      <c r="C8" s="173">
-        <v>20</v>
-      </c>
-      <c r="D8" s="173">
-        <v>30</v>
-      </c>
-      <c r="E8" s="173">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>247</v>
-      </c>
-      <c r="G8" s="173"/>
-      <c r="H8" s="173"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="169"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="173">
+      <c r="B9" s="169">
         <v>168</v>
       </c>
-      <c r="C9" s="173">
+      <c r="C9" s="169">
         <v>15</v>
       </c>
-      <c r="D9" s="173">
+      <c r="D9" s="169">
         <v>25</v>
       </c>
-      <c r="E9" s="173">
+      <c r="E9" s="169">
         <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G9" s="173"/>
-      <c r="H9" s="173"/>
+        <v>246</v>
+      </c>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
         <v>2</v>
       </c>
-      <c r="B10" s="173">
+      <c r="B10" s="169">
         <v>336</v>
       </c>
-      <c r="C10" s="173">
+      <c r="C10" s="169">
         <v>10</v>
       </c>
-      <c r="D10" s="173">
+      <c r="D10" s="169">
         <v>18</v>
       </c>
-      <c r="E10" s="173">
+      <c r="E10" s="169">
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>249</v>
-      </c>
-      <c r="G10" s="173"/>
-      <c r="H10" s="173"/>
+        <v>247</v>
+      </c>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="173">
+      <c r="B11" s="169">
         <v>504</v>
       </c>
-      <c r="C11" s="173">
+      <c r="C11" s="169">
         <v>8</v>
       </c>
-      <c r="D11" s="173">
+      <c r="D11" s="169">
         <v>15</v>
       </c>
-      <c r="E11" s="173">
+      <c r="E11" s="169">
         <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>250</v>
-      </c>
-      <c r="G11" s="173"/>
-      <c r="H11" s="173"/>
+        <v>248</v>
+      </c>
+      <c r="G11" s="169"/>
+      <c r="H11" s="169"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
         <v>4</v>
       </c>
-      <c r="B12" s="173">
+      <c r="B12" s="169">
         <v>672</v>
       </c>
-      <c r="C12" s="173">
+      <c r="C12" s="169">
         <v>5</v>
       </c>
-      <c r="D12" s="173">
+      <c r="D12" s="169">
         <v>10</v>
       </c>
-      <c r="E12" s="173">
+      <c r="E12" s="169">
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>251</v>
-      </c>
-      <c r="G12" s="173"/>
-      <c r="H12" s="173"/>
+        <v>249</v>
+      </c>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="175" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="175" t="s">
-        <v>255</v>
+      <c r="B16" s="170" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="170" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="173">
+      <c r="B17" s="169">
         <v>0</v>
       </c>
       <c r="C17">
@@ -13305,7 +13877,7 @@
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="173">
+      <c r="B18" s="169">
         <v>6</v>
       </c>
       <c r="C18">
@@ -13313,7 +13885,7 @@
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="173">
+      <c r="B19" s="169">
         <v>24</v>
       </c>
       <c r="C19">
@@ -13321,7 +13893,7 @@
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="173">
+      <c r="B20" s="169">
         <v>72</v>
       </c>
       <c r="C20">
@@ -13329,7 +13901,7 @@
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="173">
+      <c r="B21" s="169">
         <v>168</v>
       </c>
       <c r="C21">
@@ -13337,7 +13909,7 @@
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="173">
+      <c r="B22" s="169">
         <v>336</v>
       </c>
       <c r="C22">
@@ -13345,7 +13917,7 @@
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="173">
+      <c r="B23" s="169">
         <v>504</v>
       </c>
       <c r="C23">
@@ -13353,7 +13925,7 @@
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="B24" s="173">
+      <c r="B24" s="169">
         <v>672</v>
       </c>
       <c r="C24">
@@ -13362,12 +13934,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A5:A8"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13381,17 +13953,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88925FA8-23AE-49F4-9A8F-92FB9316663E}">
   <dimension ref="A1:C769"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" t="s">
         <v>254</v>
       </c>
-      <c r="B1" t="s">
-        <v>256</v>
-      </c>
       <c r="C1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/Documentación/Empresa/Control de equipos.xlsx
+++ b/Documentación/Empresa/Control de equipos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTA-Agrícola\Documents\GitHub\dta-agricola\Documentación\Empresa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\dta-agricola\Documentación\Empresa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954ED3A6-8DDE-47A0-BD01-4059C931BAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B226BB1-2065-4919-A1D5-F75A157952B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="577" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="14400" windowHeight="7270" tabRatio="577" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movimiento contínuo" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="288">
   <si>
     <t>Observaciones</t>
   </si>
@@ -852,17 +852,90 @@
   <si>
     <t>Sensor 3 gala</t>
   </si>
+  <si>
+    <t>8952020024430362948</t>
+  </si>
+  <si>
+    <t>8952020024530080316</t>
+  </si>
+  <si>
+    <t>8952020024530080324</t>
+  </si>
+  <si>
+    <t>8952020024530080332</t>
+  </si>
+  <si>
+    <t>8952020024530080407</t>
+  </si>
+  <si>
+    <t>8952020024530080415</t>
+  </si>
+  <si>
+    <t>8952020024530080423</t>
+  </si>
+  <si>
+    <t>8952020024530080431</t>
+  </si>
+  <si>
+    <t>8952020024530080449</t>
+  </si>
+  <si>
+    <t>8952020024530080456</t>
+  </si>
+  <si>
+    <t>8952020024530094119</t>
+  </si>
+  <si>
+    <t>8952020024530094127</t>
+  </si>
+  <si>
+    <t>8952020024530094134</t>
+  </si>
+  <si>
+    <t>8952020024530094135</t>
+  </si>
+  <si>
+    <t>8952020024530094143</t>
+  </si>
+  <si>
+    <t>8952020024530094150</t>
+  </si>
+  <si>
+    <t>8952020024530094267</t>
+  </si>
+  <si>
+    <t>8952020024530094275</t>
+  </si>
+  <si>
+    <t>8952020024530094283</t>
+  </si>
+  <si>
+    <t>8952020024530094291</t>
+  </si>
+  <si>
+    <t>8952020024530094309</t>
+  </si>
+  <si>
+    <t>8952020024330165126</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1144,110 +1217,110 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1256,10 +1329,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1268,16 +1341,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1289,25 +1362,25 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1319,49 +1392,49 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1370,34 +1443,34 @@
     <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1406,94 +1479,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1505,108 +1560,126 @@
     <xf numFmtId="14" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1616,14 +1689,14 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1632,25 +1705,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
@@ -1665,7 +1723,26 @@
     <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -10038,41 +10115,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="89" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="89" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="89" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="89" customWidth="1"/>
+    <col min="1" max="1" width="5.1796875" style="89" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" style="89" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" style="89" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" style="89" customWidth="1"/>
     <col min="5" max="5" width="10" style="89" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" style="89" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="89" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="89" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" style="89" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="89" customWidth="1"/>
-    <col min="11" max="11" width="37.85546875" style="89" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" style="89" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" style="89" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="89" customWidth="1"/>
-    <col min="15" max="15" width="26.140625" style="89" customWidth="1"/>
-    <col min="16" max="17" width="19.140625" style="89" customWidth="1"/>
-    <col min="18" max="18" width="60.42578125" style="90" customWidth="1"/>
-    <col min="19" max="26" width="12.140625" style="46" customWidth="1"/>
-    <col min="27" max="16384" width="11.42578125" style="89"/>
+    <col min="6" max="6" width="6.81640625" style="89" customWidth="1"/>
+    <col min="7" max="7" width="7.453125" style="89" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="89" customWidth="1"/>
+    <col min="9" max="9" width="31.453125" style="89" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="89" customWidth="1"/>
+    <col min="11" max="11" width="37.81640625" style="89" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" style="89" customWidth="1"/>
+    <col min="13" max="13" width="20.453125" style="89" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="89" customWidth="1"/>
+    <col min="15" max="15" width="26.1796875" style="89" customWidth="1"/>
+    <col min="16" max="17" width="19.1796875" style="89" customWidth="1"/>
+    <col min="18" max="18" width="60.453125" style="90" customWidth="1"/>
+    <col min="19" max="26" width="12.1796875" style="46" customWidth="1"/>
+    <col min="27" max="16384" width="11.453125" style="89"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="R1" s="171" t="s">
+      <c r="R1" s="178" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="171"/>
-      <c r="T1" s="171"/>
-      <c r="U1" s="171"/>
-      <c r="V1" s="171"/>
-      <c r="W1" s="171"/>
-      <c r="X1" s="171"/>
-      <c r="Y1" s="171"/>
-      <c r="Z1" s="171"/>
+      <c r="S1" s="178"/>
+      <c r="T1" s="178"/>
+      <c r="U1" s="178"/>
+      <c r="V1" s="178"/>
+      <c r="W1" s="178"/>
+      <c r="X1" s="178"/>
+      <c r="Y1" s="178"/>
+      <c r="Z1" s="178"/>
     </row>
     <row r="2" spans="1:26" s="37" customFormat="1">
       <c r="A2" s="37" t="s">
@@ -10214,7 +10291,7 @@
       <c r="Y3" s="65"/>
       <c r="Z3" s="65"/>
     </row>
-    <row r="4" spans="1:26" s="82" customFormat="1" ht="30">
+    <row r="4" spans="1:26" s="82" customFormat="1" ht="29">
       <c r="A4" s="82">
         <v>2</v>
       </c>
@@ -10276,7 +10353,7 @@
       <c r="Y4" s="96"/>
       <c r="Z4" s="96"/>
     </row>
-    <row r="5" spans="1:26" s="56" customFormat="1" ht="30">
+    <row r="5" spans="1:26" s="56" customFormat="1" ht="29">
       <c r="A5" s="56">
         <v>3</v>
       </c>
@@ -11137,30 +11214,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="39" customWidth="1"/>
+    <col min="1" max="1" width="5.1796875" style="39" customWidth="1"/>
     <col min="2" max="2" width="23" style="39" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="39" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" style="39" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" style="39" customWidth="1"/>
     <col min="5" max="5" width="10" style="39" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" style="39" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" style="39" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" style="39" customWidth="1"/>
+    <col min="7" max="7" width="24.453125" style="39" customWidth="1"/>
     <col min="8" max="8" width="14" style="39" customWidth="1"/>
-    <col min="9" max="9" width="39.42578125" style="39" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" style="39" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="39" customWidth="1"/>
-    <col min="12" max="12" width="22.85546875" style="39" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" style="39" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" style="39" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" style="39" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="39" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" style="39" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" style="39" customWidth="1"/>
-    <col min="19" max="19" width="10.42578125" style="39" customWidth="1"/>
-    <col min="20" max="21" width="19.140625" style="39" customWidth="1"/>
-    <col min="22" max="22" width="60.42578125" style="40" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="39"/>
+    <col min="9" max="9" width="39.453125" style="39" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" style="39" customWidth="1"/>
+    <col min="11" max="11" width="20.54296875" style="39" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" style="39" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" style="39" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="39" customWidth="1"/>
+    <col min="15" max="15" width="10.453125" style="39" customWidth="1"/>
+    <col min="16" max="16" width="10.81640625" style="39" customWidth="1"/>
+    <col min="17" max="17" width="10.453125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="10.81640625" style="39" customWidth="1"/>
+    <col min="19" max="19" width="10.453125" style="39" customWidth="1"/>
+    <col min="20" max="21" width="19.1796875" style="39" customWidth="1"/>
+    <col min="22" max="22" width="60.453125" style="40" customWidth="1"/>
+    <col min="23" max="16384" width="11.453125" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -11454,22 +11531,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" style="39" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="176" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="39" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="39" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" style="39" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" style="171" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" style="39" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" style="39" customWidth="1"/>
     <col min="5" max="5" width="10" style="39" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" style="39" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="39" customWidth="1"/>
-    <col min="8" max="8" width="38.7109375" style="39" customWidth="1"/>
-    <col min="9" max="13" width="15.42578125" style="39" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" style="39" customWidth="1"/>
-    <col min="15" max="15" width="22.85546875" style="39" customWidth="1"/>
-    <col min="16" max="17" width="10.42578125" style="39" customWidth="1"/>
-    <col min="18" max="18" width="60.42578125" style="40" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="39"/>
+    <col min="6" max="6" width="22.81640625" style="39" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="39" customWidth="1"/>
+    <col min="8" max="8" width="38.7265625" style="39" customWidth="1"/>
+    <col min="9" max="13" width="15.453125" style="39" customWidth="1"/>
+    <col min="14" max="14" width="17.453125" style="39" customWidth="1"/>
+    <col min="15" max="15" width="22.81640625" style="39" customWidth="1"/>
+    <col min="16" max="17" width="10.453125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="60.453125" style="40" customWidth="1"/>
+    <col min="19" max="16384" width="11.453125" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -11479,7 +11556,7 @@
       <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="172" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="42" t="s">
@@ -11535,7 +11612,7 @@
       <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="B3" s="178" t="s">
+      <c r="B3" s="173" t="s">
         <v>161</v>
       </c>
       <c r="C3" s="43">
@@ -11570,7 +11647,7 @@
       <c r="R3" s="51"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="B4" s="179"/>
+      <c r="B4" s="174"/>
       <c r="C4" s="43"/>
       <c r="D4" s="44"/>
       <c r="E4" s="44"/>
@@ -11584,7 +11661,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="38"/>
-      <c r="B5" s="180">
+      <c r="B5" s="175">
         <v>20333844254</v>
       </c>
       <c r="C5"/>
@@ -11597,7 +11674,7 @@
       <c r="J5" s="153" t="s">
         <v>202</v>
       </c>
-      <c r="L5" s="182" t="s">
+      <c r="L5" s="177" t="s">
         <v>262</v>
       </c>
       <c r="M5" s="161" t="s">
@@ -11607,7 +11684,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="38"/>
-      <c r="B6" s="180"/>
+      <c r="B6" s="175"/>
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
@@ -11617,7 +11694,7 @@
       <c r="K6" s="153" t="s">
         <v>260</v>
       </c>
-      <c r="L6" s="182" t="s">
+      <c r="L6" s="177" t="s">
         <v>261</v>
       </c>
       <c r="M6" s="161"/>
@@ -11630,7 +11707,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="38"/>
-      <c r="B7" s="180"/>
+      <c r="B7" s="175"/>
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
@@ -11638,7 +11715,7 @@
       <c r="I7"/>
       <c r="J7" s="153"/>
       <c r="K7" s="153"/>
-      <c r="L7" s="182" t="s">
+      <c r="L7" s="177" t="s">
         <v>261</v>
       </c>
       <c r="M7" s="161"/>
@@ -11649,7 +11726,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="38"/>
-      <c r="B8" s="180"/>
+      <c r="B8" s="175"/>
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8"/>
@@ -11657,7 +11734,7 @@
       <c r="I8"/>
       <c r="J8" s="153"/>
       <c r="K8" s="153"/>
-      <c r="L8" s="182" t="s">
+      <c r="L8" s="177" t="s">
         <v>261</v>
       </c>
       <c r="M8" s="161"/>
@@ -11668,7 +11745,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="38"/>
-      <c r="B9" s="180"/>
+      <c r="B9" s="175"/>
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
@@ -11676,7 +11753,7 @@
       <c r="I9"/>
       <c r="J9" s="153"/>
       <c r="K9" s="153"/>
-      <c r="L9" s="182" t="s">
+      <c r="L9" s="177" t="s">
         <v>261</v>
       </c>
       <c r="M9" s="161"/>
@@ -11685,7 +11762,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="38"/>
-      <c r="B10" s="180"/>
+      <c r="B10" s="175"/>
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
@@ -11693,7 +11770,7 @@
       <c r="I10"/>
       <c r="J10" s="153"/>
       <c r="K10" s="153"/>
-      <c r="L10" s="182" t="s">
+      <c r="L10" s="177" t="s">
         <v>261</v>
       </c>
       <c r="M10" s="161"/>
@@ -11701,7 +11778,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="B11" s="180">
+      <c r="B11" s="175">
         <v>24430362948</v>
       </c>
       <c r="C11"/>
@@ -11718,7 +11795,7 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="B12" s="180">
+      <c r="B12" s="175">
         <v>24530080316</v>
       </c>
       <c r="C12"/>
@@ -11741,7 +11818,7 @@
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="B13" s="180">
+      <c r="B13" s="175">
         <v>24530080324</v>
       </c>
       <c r="C13"/>
@@ -11764,7 +11841,7 @@
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="B14" s="180">
+      <c r="B14" s="175">
         <v>24530080332</v>
       </c>
       <c r="C14"/>
@@ -11785,7 +11862,7 @@
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="B15" s="180">
+      <c r="B15" s="175">
         <v>24530080407</v>
       </c>
       <c r="C15"/>
@@ -11802,7 +11879,7 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="B16" s="180">
+      <c r="B16" s="175">
         <v>24530080415</v>
       </c>
       <c r="C16"/>
@@ -11823,7 +11900,7 @@
       </c>
     </row>
     <row r="17" spans="2:14">
-      <c r="B17" s="180">
+      <c r="B17" s="175">
         <v>24530080423</v>
       </c>
       <c r="C17"/>
@@ -11844,7 +11921,7 @@
       </c>
     </row>
     <row r="18" spans="2:14">
-      <c r="B18" s="180">
+      <c r="B18" s="175">
         <v>24530080431</v>
       </c>
       <c r="C18"/>
@@ -11865,7 +11942,7 @@
       </c>
     </row>
     <row r="19" spans="2:14">
-      <c r="B19" s="180">
+      <c r="B19" s="175">
         <v>24530080449</v>
       </c>
       <c r="C19"/>
@@ -11884,7 +11961,7 @@
       <c r="N19"/>
     </row>
     <row r="20" spans="2:14">
-      <c r="B20" s="180">
+      <c r="B20" s="175">
         <v>24530080456</v>
       </c>
       <c r="C20"/>
@@ -11907,7 +11984,7 @@
       </c>
     </row>
     <row r="21" spans="2:14">
-      <c r="B21" s="180">
+      <c r="B21" s="175">
         <v>24530094119</v>
       </c>
       <c r="C21"/>
@@ -11928,7 +12005,7 @@
       </c>
     </row>
     <row r="22" spans="2:14">
-      <c r="B22" s="180">
+      <c r="B22" s="175">
         <v>24530094127</v>
       </c>
       <c r="C22"/>
@@ -11945,7 +12022,7 @@
       <c r="N22" s="160"/>
     </row>
     <row r="23" spans="2:14">
-      <c r="B23" s="181">
+      <c r="B23" s="176">
         <v>24530094134</v>
       </c>
       <c r="C23" s="163"/>
@@ -11962,7 +12039,7 @@
       </c>
     </row>
     <row r="24" spans="2:14">
-      <c r="B24" s="180">
+      <c r="B24" s="175">
         <v>24530094135</v>
       </c>
       <c r="C24"/>
@@ -11985,7 +12062,7 @@
       </c>
     </row>
     <row r="25" spans="2:14">
-      <c r="B25" s="180">
+      <c r="B25" s="175">
         <v>24530094143</v>
       </c>
       <c r="C25"/>
@@ -12006,7 +12083,7 @@
       <c r="N25"/>
     </row>
     <row r="26" spans="2:14">
-      <c r="B26" s="180">
+      <c r="B26" s="175">
         <v>24530094150</v>
       </c>
       <c r="C26"/>
@@ -12027,7 +12104,7 @@
       <c r="N26"/>
     </row>
     <row r="27" spans="2:14">
-      <c r="B27" s="180">
+      <c r="B27" s="175">
         <v>24530094267</v>
       </c>
       <c r="C27"/>
@@ -12048,7 +12125,7 @@
       <c r="N27"/>
     </row>
     <row r="28" spans="2:14">
-      <c r="B28" s="180">
+      <c r="B28" s="175">
         <v>24530094275</v>
       </c>
       <c r="C28"/>
@@ -12071,7 +12148,7 @@
       </c>
     </row>
     <row r="29" spans="2:14">
-      <c r="B29" s="180">
+      <c r="B29" s="175">
         <v>24530094283</v>
       </c>
       <c r="C29"/>
@@ -12094,7 +12171,7 @@
       </c>
     </row>
     <row r="30" spans="2:14">
-      <c r="B30" s="180">
+      <c r="B30" s="175">
         <v>24530094291</v>
       </c>
       <c r="C30"/>
@@ -12117,7 +12194,7 @@
       </c>
     </row>
     <row r="31" spans="2:14">
-      <c r="B31" s="180">
+      <c r="B31" s="175">
         <v>24530094309</v>
       </c>
       <c r="C31"/>
@@ -12151,25 +12228,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.85546875" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.81640625" customWidth="1"/>
+    <col min="6" max="6" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" customWidth="1"/>
+    <col min="8" max="8" width="7.81640625" customWidth="1"/>
+    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30">
+    <row r="1" spans="1:14">
       <c r="A1" s="22" t="s">
         <v>2</v>
       </c>
@@ -12213,7 +12290,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
+    <row r="2" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
       <c r="A2" s="26" t="s">
         <v>87</v>
       </c>
@@ -12239,7 +12316,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
+    <row r="3" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>161</v>
       </c>
@@ -12265,7 +12342,7 @@
         <v>45904</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
+    <row r="4" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
       <c r="A4" s="167" t="s">
         <v>233</v>
       </c>
@@ -12291,8 +12368,8 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="19" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:14" s="19" customFormat="1" ht="14.15" customHeight="1">
+      <c r="A5" s="185" t="s">
         <v>140</v>
       </c>
       <c r="B5" s="27">
@@ -12315,8 +12392,8 @@
       <c r="H6" s="160"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7">
-        <v>20333844254</v>
+      <c r="A7" s="183" t="s">
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>175</v>
@@ -12332,14 +12409,14 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8">
-        <v>24430362948</v>
+      <c r="A8" s="183" t="s">
+        <v>266</v>
       </c>
       <c r="E8" t="s">
         <v>175</v>
       </c>
       <c r="H8" s="160"/>
-      <c r="I8" s="157" t="s">
+      <c r="I8" s="186" t="s">
         <v>223</v>
       </c>
       <c r="J8">
@@ -12347,8 +12424,8 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9">
-        <v>24530080316</v>
+      <c r="A9" s="183" t="s">
+        <v>267</v>
       </c>
       <c r="E9" t="s">
         <v>175</v>
@@ -12370,8 +12447,8 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10">
-        <v>24530080324</v>
+      <c r="A10" s="183" t="s">
+        <v>268</v>
       </c>
       <c r="E10" t="s">
         <v>175</v>
@@ -12390,8 +12467,8 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11">
-        <v>24530080332</v>
+      <c r="A11" s="183" t="s">
+        <v>269</v>
       </c>
       <c r="E11" t="s">
         <v>175</v>
@@ -12414,8 +12491,8 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12">
-        <v>24530080407</v>
+      <c r="A12" s="183" t="s">
+        <v>270</v>
       </c>
       <c r="E12" t="s">
         <v>175</v>
@@ -12429,8 +12506,8 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13">
-        <v>24530080415</v>
+      <c r="A13" s="183" t="s">
+        <v>271</v>
       </c>
       <c r="E13" t="s">
         <v>175</v>
@@ -12450,8 +12527,8 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14">
-        <v>24530080423</v>
+      <c r="A14" s="183" t="s">
+        <v>272</v>
       </c>
       <c r="E14" t="s">
         <v>175</v>
@@ -12471,8 +12548,8 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15">
-        <v>24530080431</v>
+      <c r="A15" s="183" t="s">
+        <v>273</v>
       </c>
       <c r="E15" t="s">
         <v>175</v>
@@ -12492,8 +12569,8 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16">
-        <v>24530080449</v>
+      <c r="A16" s="183" t="s">
+        <v>274</v>
       </c>
       <c r="E16" t="s">
         <v>175</v>
@@ -12507,8 +12584,8 @@
       <c r="H16" s="160"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17">
-        <v>24530080456</v>
+      <c r="A17" s="183" t="s">
+        <v>275</v>
       </c>
       <c r="E17" t="s">
         <v>175</v>
@@ -12530,8 +12607,8 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18">
-        <v>24530094119</v>
+      <c r="A18" s="183" t="s">
+        <v>276</v>
       </c>
       <c r="E18" t="s">
         <v>175</v>
@@ -12551,8 +12628,8 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19">
-        <v>24530094127</v>
+      <c r="A19" s="183" t="s">
+        <v>277</v>
       </c>
       <c r="E19" t="s">
         <v>175</v>
@@ -12567,8 +12644,8 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="163">
-        <v>24530094134</v>
+      <c r="A20" s="184" t="s">
+        <v>278</v>
       </c>
       <c r="B20" s="163"/>
       <c r="C20" s="163"/>
@@ -12591,8 +12668,8 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21">
-        <v>24530094135</v>
+      <c r="A21" s="183" t="s">
+        <v>279</v>
       </c>
       <c r="E21" t="s">
         <v>175</v>
@@ -12611,8 +12688,8 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22">
-        <v>24530094143</v>
+      <c r="A22" s="183" t="s">
+        <v>280</v>
       </c>
       <c r="E22" t="s">
         <v>175</v>
@@ -12628,8 +12705,8 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23">
-        <v>24530094150</v>
+      <c r="A23" s="183" t="s">
+        <v>281</v>
       </c>
       <c r="E23" t="s">
         <v>175</v>
@@ -12645,8 +12722,8 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24">
-        <v>24530094267</v>
+      <c r="A24" s="183" t="s">
+        <v>282</v>
       </c>
       <c r="E24" t="s">
         <v>175</v>
@@ -12662,8 +12739,8 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25">
-        <v>24530094275</v>
+      <c r="A25" s="183" t="s">
+        <v>283</v>
       </c>
       <c r="E25" t="s">
         <v>175</v>
@@ -12682,8 +12759,8 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26">
-        <v>24530094283</v>
+      <c r="A26" s="183" t="s">
+        <v>284</v>
       </c>
       <c r="E26" t="s">
         <v>175</v>
@@ -12705,8 +12782,8 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27">
-        <v>24530094291</v>
+      <c r="A27" s="183" t="s">
+        <v>285</v>
       </c>
       <c r="E27" t="s">
         <v>175</v>
@@ -12725,8 +12802,8 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28">
-        <v>24530094309</v>
+      <c r="A28" s="183" t="s">
+        <v>286</v>
       </c>
       <c r="E28" t="s">
         <v>175</v>
@@ -12748,8 +12825,8 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30">
-        <v>24330165126</v>
+      <c r="A30" s="183" t="s">
+        <v>287</v>
       </c>
       <c r="E30" t="s">
         <v>175</v>
@@ -12819,7 +12896,7 @@
     <row r="49" spans="1:9">
       <c r="I49" s="153"/>
     </row>
-    <row r="51" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="51" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A51" s="18" t="s">
         <v>18</v>
       </c>
@@ -12848,7 +12925,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="52" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A52" s="24" t="s">
         <v>39</v>
       </c>
@@ -12877,7 +12954,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="53" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A53" s="24" t="s">
         <v>94</v>
       </c>
@@ -12906,7 +12983,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="54" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A54" s="24" t="s">
         <v>50</v>
       </c>
@@ -12935,7 +13012,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="55" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A55" s="24" t="s">
         <v>30</v>
       </c>
@@ -12964,7 +13041,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="56" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A56" s="24" t="s">
         <v>56</v>
       </c>
@@ -12993,7 +13070,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="57" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A57" s="24" t="s">
         <v>45</v>
       </c>
@@ -13022,7 +13099,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="58" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A58" s="24" t="s">
         <v>153</v>
       </c>
@@ -13048,7 +13125,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="59" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A59" s="18" t="s">
         <v>118</v>
       </c>
@@ -13068,7 +13145,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="18" customFormat="1" ht="14.1" customHeight="1">
+    <row r="60" spans="1:9" s="18" customFormat="1" ht="14.15" customHeight="1">
       <c r="A60" s="18" t="s">
         <v>147</v>
       </c>
@@ -13091,7 +13168,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="20" customFormat="1" ht="14.1" customHeight="1">
+    <row r="62" spans="1:9" s="20" customFormat="1" ht="14.15" customHeight="1">
       <c r="A62" s="29" t="s">
         <v>110</v>
       </c>
@@ -13114,7 +13191,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="20" customFormat="1" ht="14.1" customHeight="1">
+    <row r="63" spans="1:9" s="20" customFormat="1" ht="14.15" customHeight="1">
       <c r="A63" s="29" t="s">
         <v>99</v>
       </c>
@@ -13137,7 +13214,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="20" customFormat="1" ht="14.1" customHeight="1">
+    <row r="64" spans="1:9" s="20" customFormat="1" ht="14.15" customHeight="1">
       <c r="A64" s="29" t="s">
         <v>80</v>
       </c>
@@ -13156,7 +13233,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="21" customFormat="1" ht="14.1" customHeight="1">
+    <row r="65" spans="1:9" s="21" customFormat="1" ht="14.15" customHeight="1">
       <c r="A65" s="32" t="s">
         <v>61</v>
       </c>
@@ -13182,7 +13259,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="66" spans="1:9" s="21" customFormat="1" ht="14.1" customHeight="1">
+    <row r="66" spans="1:9" s="21" customFormat="1" ht="14.15" customHeight="1">
       <c r="A66" s="21" t="s">
         <v>122</v>
       </c>
@@ -13203,7 +13280,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -13212,14 +13289,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -13242,7 +13319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" ht="15">
       <c r="A2" s="4" t="s">
         <v>186</v>
       </c>
@@ -13262,7 +13339,7 @@
         <v>43872</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="8" t="s">
         <v>186</v>
       </c>
@@ -13282,7 +13359,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="4" t="s">
         <v>186</v>
       </c>
@@ -13302,7 +13379,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="8" t="s">
         <v>186</v>
       </c>
@@ -13322,7 +13399,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="15">
       <c r="A6" s="4" t="s">
         <v>186</v>
       </c>
@@ -13342,7 +13419,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="15">
       <c r="A7" s="8" t="s">
         <v>186</v>
       </c>
@@ -13362,7 +13439,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="15">
       <c r="A8" s="4" t="s">
         <v>186</v>
       </c>
@@ -13382,7 +13459,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="15">
       <c r="A9" s="8" t="s">
         <v>187</v>
       </c>
@@ -13400,7 +13477,7 @@
         <v>44384</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="15">
       <c r="A10" s="4" t="s">
         <v>186</v>
       </c>
@@ -13420,7 +13497,7 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="15">
       <c r="A11" s="8" t="s">
         <v>186</v>
       </c>
@@ -13440,7 +13517,7 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" ht="15">
       <c r="A12" s="4" t="s">
         <v>186</v>
       </c>
@@ -13460,7 +13537,7 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="15">
       <c r="A13" s="8" t="s">
         <v>186</v>
       </c>
@@ -13480,7 +13557,7 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" ht="15">
       <c r="A14" s="4" t="s">
         <v>186</v>
       </c>
@@ -13500,7 +13577,7 @@
         <v>44762</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="15">
       <c r="A15" s="8" t="s">
         <v>186</v>
       </c>
@@ -13520,7 +13597,7 @@
         <v>44647</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="15">
       <c r="A16" s="4" t="s">
         <v>186</v>
       </c>
@@ -13540,7 +13617,7 @@
         <v>44647</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15">
       <c r="A17" s="8" t="s">
         <v>186</v>
       </c>
@@ -13556,7 +13633,7 @@
       </c>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="15">
       <c r="A18" s="4" t="s">
         <v>187</v>
       </c>
@@ -13572,7 +13649,7 @@
       </c>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" ht="15">
       <c r="A19" s="8" t="s">
         <v>186</v>
       </c>
@@ -13588,7 +13665,7 @@
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" ht="15">
       <c r="A20" s="4" t="s">
         <v>187</v>
       </c>
@@ -13602,7 +13679,7 @@
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" ht="15">
       <c r="A21" s="8" t="s">
         <v>187</v>
       </c>
@@ -13642,41 +13719,41 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D02258-BB1F-41F1-B649-95B4395F579C}">
   <dimension ref="A2:H24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="55.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" customWidth="1"/>
+    <col min="3" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="55.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="21">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="182" t="s">
         <v>250</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="181" t="s">
         <v>251</v>
       </c>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="181" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="172" t="s">
+      <c r="C3" s="180" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172" t="s">
+      <c r="D3" s="180"/>
+      <c r="E3" s="180"/>
+      <c r="F3" s="180" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
+      <c r="A4" s="181"/>
+      <c r="B4" s="181"/>
       <c r="C4" s="154" t="s">
         <v>238</v>
       </c>
@@ -13686,12 +13763,12 @@
       <c r="E4" s="154" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="172"/>
+      <c r="F4" s="180"/>
       <c r="G4" s="168"/>
       <c r="H4" s="168"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="175">
+      <c r="A5" s="179">
         <v>0</v>
       </c>
       <c r="B5" s="169">
@@ -13713,7 +13790,7 @@
       <c r="H5" s="169"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="175"/>
+      <c r="A6" s="179"/>
       <c r="B6" s="169">
         <v>6</v>
       </c>
@@ -13733,7 +13810,7 @@
       <c r="H6" s="169"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="175"/>
+      <c r="A7" s="179"/>
       <c r="B7" s="169">
         <v>24</v>
       </c>
@@ -13753,7 +13830,7 @@
       <c r="H7" s="169"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="175"/>
+      <c r="A8" s="179"/>
       <c r="B8" s="169">
         <v>72</v>
       </c>
@@ -13953,7 +14030,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88925FA8-23AE-49F4-9A8F-92FB9316663E}">
   <dimension ref="A1:C769"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
